--- a/templates/taiwan/template.xlsx
+++ b/templates/taiwan/template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="PN" sheetId="6" r:id="rId1"/>
@@ -1586,6 +1586,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <charset val="136"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF8DC63F"/>
@@ -1594,19 +1600,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <charset val="136"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>

--- a/templates/taiwan/template.xlsx
+++ b/templates/taiwan/template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="PN" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="145">
   <si>
     <t>NNRoad – Employer of Record, Payroll Worldwide</t>
   </si>
@@ -78,31 +78,16 @@
     <t>Company name:</t>
   </si>
   <si>
-    <t>Coral Sea</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
     <t>Client ID:</t>
   </si>
   <si>
-    <t>CUS1516</t>
-  </si>
-  <si>
     <t>Invoice number</t>
   </si>
   <si>
-    <t>PN-CUS1516-031120261</t>
-  </si>
-  <si>
     <t>Address:</t>
-  </si>
-  <si>
-    <t>4205/41 Williams Esplanade, PALM COVE, QLD, Australia</t>
   </si>
   <si>
     <t>Invoice date</t>
@@ -177,6 +162,9 @@
     <t>3. This is a computer generated document.  No Signature required.</t>
   </si>
   <si>
+    <t>TW</t>
+  </si>
+  <si>
     <t>Pay Period</t>
   </si>
   <si>
@@ -288,6 +276,9 @@
     <t xml:space="preserve">Invoice adjustment </t>
   </si>
   <si>
+    <t>TW EE</t>
+  </si>
+  <si>
     <t>EE</t>
   </si>
   <si>
@@ -335,15 +326,6 @@
   </si>
   <si>
     <t>EOR/PEO(NTD)</t>
-  </si>
-  <si>
-    <t>CUS1516-0001</t>
-  </si>
-  <si>
-    <t>CUS1516-0002</t>
-  </si>
-  <si>
-    <t>CUS1516-0003</t>
   </si>
   <si>
     <t>NNRoad</t>
@@ -3364,63 +3346,48 @@
       <c r="A8" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="126" t="s">
-        <v>6</v>
-      </c>
+      <c r="B8" s="126"/>
       <c r="C8" s="127"/>
       <c r="D8" s="125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="125"/>
-      <c r="F8" s="126" t="s">
-        <v>8</v>
-      </c>
+      <c r="F8" s="126"/>
       <c r="G8" s="128"/>
     </row>
     <row r="9" s="112" customFormat="1" ht="13" customHeight="1" spans="1:8">
       <c r="A9" s="125" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="126" t="s">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B9" s="126"/>
       <c r="C9" s="129"/>
       <c r="D9" s="125" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" s="125"/>
-      <c r="F9" s="126" t="s">
-        <v>12</v>
-      </c>
+      <c r="F9" s="126"/>
       <c r="G9" s="128"/>
     </row>
     <row r="10" s="111" customFormat="1" ht="13" customHeight="1" spans="1:8">
       <c r="A10" s="125" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="130" t="s">
-        <v>14</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B10" s="130"/>
       <c r="C10" s="129"/>
       <c r="D10" s="125" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E10" s="125"/>
-      <c r="F10" s="131">
-        <f ca="1">TODAY()</f>
-        <v>46230</v>
-      </c>
+      <c r="F10" s="131"/>
       <c r="G10" s="120"/>
     </row>
     <row r="11" s="112" customFormat="1" ht="12" customHeight="1" spans="1:8">
       <c r="A11" s="132"/>
       <c r="D11" s="125" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E11" s="125"/>
-      <c r="F11" s="131">
-        <v>46099</v>
-      </c>
+      <c r="F11" s="131"/>
       <c r="G11" s="128"/>
     </row>
     <row r="12" s="111" customFormat="1" ht="12" customHeight="1" spans="1:8">
@@ -3434,7 +3401,7 @@
     <row r="13" ht="12" customHeight="1"/>
     <row r="14" s="113" customFormat="1" ht="28" customHeight="1" spans="1:8">
       <c r="A14" s="135" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B14" s="136"/>
       <c r="C14" s="136"/>
@@ -3444,13 +3411,13 @@
         <v>Amount (NTD)</v>
       </c>
       <c r="F14" s="138" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G14" s="139"/>
     </row>
     <row r="15" s="114" customFormat="1" ht="16" customHeight="1" spans="1:8">
       <c r="A15" s="140" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D15" s="141"/>
       <c r="E15" s="142">
@@ -3482,7 +3449,7 @@
     <row r="17" s="115" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A17" s="145" t="str">
         <f>"- Labor cost for "&amp;TW!B10&amp;"  -  "&amp;MONTH(TW!$B$2)&amp;"-"&amp;YEAR(TW!$B$2)</f>
-        <v>- Labor cost for 0  -  1-1900</v>
+        <v>- Labor cost for   -  1-1900</v>
       </c>
       <c r="D17" s="146"/>
       <c r="E17" s="147">
@@ -3498,7 +3465,7 @@
     <row r="18" s="115" customFormat="1" ht="12.75" customHeight="1" spans="1:7">
       <c r="A18" s="145" t="str">
         <f>"- Labor cost for "&amp;TW!B11&amp;"  -  "&amp;MONTH(TW!$B$2)&amp;"-"&amp;YEAR(TW!$B$2)</f>
-        <v>- Labor cost for 0  -  1-1900</v>
+        <v>- Labor cost for   -  1-1900</v>
       </c>
       <c r="D18" s="146"/>
       <c r="E18" s="147">
@@ -3530,7 +3497,7 @@
     <row r="20" ht="12.75" customHeight="1" spans="1:7">
       <c r="A20" s="145" t="str">
         <f>"- "&amp;+"Expense claim for "&amp;TW!B10</f>
-        <v>- Expense claim for 0</v>
+        <v>- Expense claim for </v>
       </c>
       <c r="D20" s="151"/>
       <c r="E20" s="147">
@@ -3546,7 +3513,7 @@
     <row r="21" ht="12.75" customHeight="1" spans="1:7">
       <c r="A21" s="145" t="str">
         <f>"- "&amp;+"Expense claim for "&amp;TW!B11</f>
-        <v>- Expense claim for 0</v>
+        <v>- Expense claim for </v>
       </c>
       <c r="D21" s="151"/>
       <c r="E21" s="147">
@@ -3568,16 +3535,16 @@
     </row>
     <row r="23" s="116" customFormat="1" ht="16" customHeight="1" spans="1:7">
       <c r="A23" s="140" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D23" s="141"/>
       <c r="E23" s="142">
         <f>SUM(E24:E25)</f>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="F23" s="155">
         <f>SUM(F24:F25)</f>
-        <v>431.341600181483</v>
+        <v>143.780533393828</v>
       </c>
       <c r="G23" s="156"/>
     </row>
@@ -3589,11 +3556,11 @@
       <c r="D24" s="158"/>
       <c r="E24" s="154">
         <f>TW!G6</f>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="F24" s="148">
         <f>E24/$B$31</f>
-        <v>431.341600181483</v>
+        <v>143.780533393828</v>
       </c>
       <c r="G24" s="150"/>
     </row>
@@ -3620,18 +3587,18 @@
     </row>
     <row r="28" s="114" customFormat="1" ht="15" customHeight="1" spans="1:7">
       <c r="A28" s="163" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B28" s="164"/>
       <c r="C28" s="164"/>
       <c r="D28" s="164"/>
       <c r="E28" s="165">
         <f>E15+E23</f>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="F28" s="166">
         <f>F15+F23</f>
-        <v>431.341600181483</v>
+        <v>143.780533393828</v>
       </c>
       <c r="G28" s="144"/>
     </row>
@@ -3663,12 +3630,12 @@
       </c>
       <c r="C31" s="169"/>
       <c r="D31" s="174" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E31" s="175"/>
       <c r="F31" s="176">
         <f>F28</f>
-        <v>431.341600181483</v>
+        <v>143.780533393828</v>
       </c>
       <c r="G31" s="150"/>
     </row>
@@ -3677,7 +3644,7 @@
       <c r="B32" s="177"/>
       <c r="C32" s="169"/>
       <c r="D32" s="178" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F32" s="179">
         <f>TW!E22</f>
@@ -3690,7 +3657,7 @@
       <c r="B33" s="177"/>
       <c r="C33" s="169"/>
       <c r="D33" s="178" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F33" s="179">
         <f>TW!E23</f>
@@ -3703,7 +3670,7 @@
       <c r="B34" s="177"/>
       <c r="C34" s="169"/>
       <c r="D34" s="178" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F34" s="179">
         <f>TW!E24</f>
@@ -3716,7 +3683,7 @@
       <c r="B35" s="177"/>
       <c r="C35" s="180"/>
       <c r="D35" s="181" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E35" s="182"/>
       <c r="F35" s="183">
@@ -3730,11 +3697,11 @@
       <c r="B36" s="177"/>
       <c r="C36" s="169"/>
       <c r="D36" s="184" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F36" s="185">
         <f>SUM(F31:F35)</f>
-        <v>441.341600181483</v>
+        <v>153.780533393828</v>
       </c>
       <c r="G36" s="150"/>
     </row>
@@ -3743,7 +3710,7 @@
       <c r="B37" s="177"/>
       <c r="C37" s="169"/>
       <c r="D37" s="186" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F37" s="185">
         <f>ROUNDUP(TW!F6/PN!B31,2)+0.01</f>
@@ -3756,12 +3723,12 @@
       <c r="B38" s="187"/>
       <c r="C38" s="169"/>
       <c r="D38" s="188" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E38" s="189"/>
       <c r="F38" s="190">
         <f>SUM(F36:F37)</f>
-        <v>441.351600181483</v>
+        <v>153.790533393828</v>
       </c>
       <c r="G38" s="150"/>
       <c r="H38" s="191"/>
@@ -3789,26 +3756,26 @@
     </row>
     <row r="42" ht="19" customHeight="1" spans="1:8">
       <c r="A42" s="192" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" ht="61" customHeight="1" spans="1:8">
       <c r="A43" s="193" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C43" s="194"/>
       <c r="D43" s="195" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="117" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" ht="11" customHeight="1" spans="1:8">
       <c r="A45" s="114" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B45" s="114"/>
       <c r="C45" s="114"/>
@@ -3818,12 +3785,12 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="114" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="114" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -3900,14 +3867,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:29">
-      <c r="A1" s="56" t="str">
-        <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,256)</f>
-        <v>TW</v>
+      <c r="A1" s="56" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:29">
       <c r="A2" s="56" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B2" s="93">
         <f>'TW-L'!C4</f>
@@ -3918,23 +3884,23 @@
         <v>0</v>
       </c>
       <c r="E2" s="61" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" s="54" customFormat="1" spans="1:29">
       <c r="E3" s="94" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F3" s="65" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G3" s="65" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H3" s="66"/>
       <c r="I3" s="67"/>
       <c r="J3" s="95" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K3" s="66"/>
       <c r="L3" s="66"/>
@@ -3952,11 +3918,11 @@
       <c r="X3" s="66"/>
       <c r="Y3" s="67"/>
       <c r="Z3" s="96" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AA3" s="66"/>
       <c r="AB3" s="95" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AC3" s="67"/>
     </row>
@@ -3964,73 +3930,73 @@
       <c r="E4" s="69"/>
       <c r="F4" s="72"/>
       <c r="G4" s="97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="98" t="s">
+        <v>41</v>
+      </c>
+      <c r="K4" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="71" t="s">
+      <c r="M4" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="71" t="s">
+      <c r="N4" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="K4" s="71" t="s">
+      <c r="O4" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="71" t="s">
+      <c r="P4" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="71" t="s">
+      <c r="Q4" s="71" t="s">
         <v>50</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="R4" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="71" t="s">
+      <c r="S4" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="P4" s="71" t="s">
+      <c r="T4" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="71" t="s">
+      <c r="U4" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="71" t="s">
+      <c r="V4" s="71" t="s">
         <v>55</v>
       </c>
-      <c r="S4" s="71" t="s">
+      <c r="W4" s="71" t="s">
         <v>56</v>
       </c>
-      <c r="T4" s="71" t="s">
+      <c r="X4" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="U4" s="71" t="s">
+      <c r="Y4" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="V4" s="71" t="s">
+      <c r="Z4" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA4" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="W4" s="71" t="s">
+      <c r="AB4" s="98" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC4" s="99" t="s">
         <v>60</v>
-      </c>
-      <c r="X4" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y4" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z4" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB4" s="98" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC4" s="99" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="5" s="54" customFormat="1" ht="15" customHeight="1" spans="1:29">
@@ -4064,14 +4030,14 @@
     <row r="6" s="55" customFormat="1" spans="1:29">
       <c r="A6" s="77"/>
       <c r="B6" s="55" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E6" s="81">
         <f t="shared" ref="E6:AC6" si="0">SUM(E9:E17)</f>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="F6" s="82">
         <f t="shared" si="0"/>
@@ -4079,11 +4045,11 @@
       </c>
       <c r="G6" s="82">
         <f t="shared" si="0"/>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="H6" s="82">
         <f t="shared" si="0"/>
-        <v>13500</v>
+        <v>4500</v>
       </c>
       <c r="I6" s="82">
         <f t="shared" si="0"/>
@@ -4234,9 +4200,9 @@
         <f>'TW-L'!C9</f>
         <v>0</v>
       </c>
-      <c r="C9" s="55" t="str">
+      <c r="C9" s="55">
         <f>'TW EE'!D10</f>
-        <v>CUS1516-0001</v>
+        <v>0</v>
       </c>
       <c r="E9" s="81">
         <f>SUM(F9:G9)+J9+Z9+AB9</f>
@@ -4337,217 +4303,63 @@
     </row>
     <row r="10" s="55" customFormat="1" spans="1:29">
       <c r="A10" s="77"/>
-      <c r="B10" s="55">
-        <f>'TW-L'!C10</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="55" t="str">
-        <f>'TW EE'!D11</f>
-        <v>CUS1516-0002</v>
-      </c>
-      <c r="E10" s="81">
-        <f>SUM(F10:G10)+J10+Z10+AB10</f>
-        <v>4500</v>
-      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="E10" s="81"/>
       <c r="F10" s="100"/>
-      <c r="G10" s="82">
-        <f>SUM(H10:I10)</f>
-        <v>4500</v>
-      </c>
-      <c r="H10" s="82">
-        <f>MAX(4500,(J10+Z10)*12%)</f>
-        <v>4500</v>
-      </c>
-      <c r="I10" s="82">
-        <f>IF(AB10&gt;0,1500,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="82">
-        <f>SUM(K10:Y10)</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="82">
-        <f>'TW-L'!N10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="82">
-        <v>0</v>
-      </c>
-      <c r="M10" s="82">
-        <f>'TW-L'!AC10</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="82">
-        <f>'TW-L'!O10</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="82">
-        <f>'TW-L'!P10</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="82">
-        <f>'TW-L'!Q10</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="82">
-        <f>'TW-L'!R10</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="82">
-        <f>'TW-L'!R10</f>
-        <v>0</v>
-      </c>
-      <c r="S10" s="82">
-        <f>'TW-L'!U10</f>
-        <v>0</v>
-      </c>
-      <c r="T10" s="82">
-        <f>'TW-L'!V10</f>
-        <v>0</v>
-      </c>
-      <c r="U10" s="82">
-        <f>'TW-L'!W10</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="82">
-        <f>'TW-L'!X10</f>
-        <v>0</v>
-      </c>
-      <c r="W10" s="82">
-        <f>'TW-L'!Y10</f>
-        <v>0</v>
-      </c>
-      <c r="X10" s="82">
-        <f>'TW-L'!AA10</f>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="82">
-        <f>'TW-L'!AB10</f>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="82">
-        <f>SUM(AA10:AA10)</f>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="82">
-        <f>'TW-L'!BL10</f>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="82">
-        <f>SUM(AC10:AC10)</f>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="83">
-        <f>'TW-L'!Z10</f>
-        <v>0</v>
-      </c>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="82"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="82"/>
+      <c r="L10" s="82"/>
+      <c r="M10" s="82"/>
+      <c r="N10" s="82"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="82"/>
+      <c r="Q10" s="82"/>
+      <c r="R10" s="82"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="82"/>
+      <c r="AC10" s="83"/>
     </row>
     <row r="11" s="55" customFormat="1" spans="1:29">
       <c r="A11" s="77"/>
-      <c r="B11" s="55">
-        <f>'TW-L'!C11</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="55" t="str">
-        <f>'TW EE'!D12</f>
-        <v>CUS1516-0003</v>
-      </c>
-      <c r="E11" s="81">
-        <f>SUM(F11:G11)+J11+Z11+AB11</f>
-        <v>4500</v>
-      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="E11" s="81"/>
       <c r="F11" s="100"/>
-      <c r="G11" s="82">
-        <f>SUM(H11:I11)</f>
-        <v>4500</v>
-      </c>
-      <c r="H11" s="82">
-        <f>MAX(4500,(J11+Z11)*12%)</f>
-        <v>4500</v>
-      </c>
-      <c r="I11" s="82">
-        <f>IF(AB11&gt;0,1500,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="82">
-        <f>SUM(K11:Y11)</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="82">
-        <f>'TW-L'!N11</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="82">
-        <v>0</v>
-      </c>
-      <c r="M11" s="82">
-        <f>'TW-L'!AC11</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="82">
-        <f>'TW-L'!O11</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="82">
-        <f>'TW-L'!P11</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="82">
-        <f>'TW-L'!Q11</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="82">
-        <f>'TW-L'!R11</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="82">
-        <f>'TW-L'!R11</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="82">
-        <f>'TW-L'!U11</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="82">
-        <f>'TW-L'!V11</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="82">
-        <f>'TW-L'!W11</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="82">
-        <f>'TW-L'!X11</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="82">
-        <f>'TW-L'!Y11</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="82">
-        <f>'TW-L'!AA11</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="82">
-        <f>'TW-L'!AB11</f>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="82">
-        <f>SUM(AA11:AA11)</f>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="82">
-        <f>'TW-L'!BL11</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="82">
-        <f>SUM(AC11:AC11)</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="83">
-        <f>'TW-L'!Z11</f>
-        <v>0</v>
-      </c>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="83"/>
     </row>
     <row r="12" s="55" customFormat="1" spans="1:29">
       <c r="A12" s="77"/>
@@ -4720,7 +4532,7 @@
     <row r="20" ht="15" customHeight="1"/>
     <row r="21" spans="1:29">
       <c r="A21" s="56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B21" s="103"/>
       <c r="C21" s="103"/>
@@ -4736,7 +4548,7 @@
     </row>
     <row r="22" spans="1:29">
       <c r="B22" s="103" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C22" s="103"/>
       <c r="D22" s="103"/>
@@ -4745,7 +4557,7 @@
     </row>
     <row r="23" spans="1:29">
       <c r="B23" s="103" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C23" s="103"/>
       <c r="D23" s="103"/>
@@ -4756,7 +4568,7 @@
     </row>
     <row r="24" spans="1:29">
       <c r="B24" s="103" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C24" s="103"/>
       <c r="D24" s="103"/>
@@ -4767,7 +4579,7 @@
     </row>
     <row r="25" spans="1:29">
       <c r="B25" s="103" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C25" s="103"/>
       <c r="D25" s="103"/>
@@ -4779,7 +4591,7 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:29">
       <c r="B26" s="103" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C26" s="103"/>
       <c r="D26" s="103"/>
@@ -4841,9 +4653,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" spans="1:33">
-      <c r="A1" s="56" t="str">
-        <f ca="1">MID(CELL("filename",A1),FIND("]",CELL("filename",A1))+1,256)</f>
-        <v>TW EE</v>
+      <c r="A1" s="56" t="s">
+        <v>66</v>
       </c>
       <c r="H1" s="58"/>
     </row>
@@ -4855,31 +4666,31 @@
       <c r="E2" s="60"/>
       <c r="F2" s="60"/>
       <c r="H2" s="61" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" s="54" customFormat="1" spans="1:33">
       <c r="B3" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="62" t="s">
-        <v>74</v>
-      </c>
       <c r="F3" s="63" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G3" s="64"/>
       <c r="H3" s="62" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I3" s="65" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="J3" s="66"/>
       <c r="K3" s="66"/>
@@ -4897,21 +4708,21 @@
       <c r="W3" s="66"/>
       <c r="X3" s="67"/>
       <c r="Y3" s="65" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Z3" s="67"/>
       <c r="AA3" s="65" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AB3" s="66"/>
       <c r="AC3" s="66"/>
       <c r="AD3" s="66"/>
       <c r="AE3" s="67"/>
       <c r="AF3" s="65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AG3" s="68" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" s="54" customFormat="1" ht="57.75" customHeight="1" spans="1:33">
@@ -4920,80 +4731,80 @@
       <c r="D4" s="69"/>
       <c r="E4" s="69"/>
       <c r="F4" s="70" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G4" s="70" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H4" s="69"/>
       <c r="I4" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="71" t="s">
+      <c r="L4" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="K4" s="71" t="s">
+      <c r="O4" s="71" t="s">
         <v>49</v>
       </c>
-      <c r="L4" s="71" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4" s="71" t="s">
+      <c r="P4" s="71" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q4" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="71" t="s">
+      <c r="R4" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="71" t="s">
+      <c r="S4" s="71" t="s">
         <v>53</v>
       </c>
-      <c r="P4" s="71" t="s">
+      <c r="T4" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="U4" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="V4" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="W4" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="X4" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y4" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z4" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA4" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB4" s="71" t="s">
+        <v>78</v>
+      </c>
+      <c r="AC4" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD4" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="Q4" s="71" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="71" t="s">
-        <v>58</v>
-      </c>
-      <c r="U4" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="V4" s="71" t="s">
-        <v>60</v>
-      </c>
-      <c r="W4" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA4" s="71" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB4" s="71" t="s">
+      <c r="AE4" s="71" t="s">
         <v>81</v>
-      </c>
-      <c r="AC4" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD4" s="71" t="s">
-        <v>83</v>
-      </c>
-      <c r="AE4" s="71" t="s">
-        <v>84</v>
       </c>
       <c r="AF4" s="72"/>
       <c r="AG4" s="73"/>
@@ -5029,7 +4840,7 @@
     </row>
     <row r="6" s="55" customFormat="1" spans="1:33">
       <c r="A6" s="77" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H6" s="78"/>
       <c r="I6" s="79"/>
@@ -5153,16 +4964,13 @@
     </row>
     <row r="10" s="55" customFormat="1" spans="1:33">
       <c r="A10" s="77"/>
-      <c r="B10" s="55" t="str">
+      <c r="B10" s="55">
         <f>PN!$B$9</f>
-        <v>CUS1516</v>
-      </c>
-      <c r="C10" s="55" t="str">
+        <v>0</v>
+      </c>
+      <c r="C10" s="55">
         <f>PN!$B$8</f>
-        <v>Coral Sea</v>
-      </c>
-      <c r="D10" s="55" t="s">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E10" s="86">
         <f>'TW-L'!C9</f>
@@ -5281,259 +5089,73 @@
     </row>
     <row r="11" s="55" customFormat="1" spans="1:33">
       <c r="A11" s="77"/>
-      <c r="B11" s="55" t="str">
-        <f>PN!$B$9</f>
-        <v>CUS1516</v>
-      </c>
-      <c r="C11" s="55" t="str">
-        <f>PN!B8</f>
-        <v>Coral Sea</v>
-      </c>
-      <c r="D11" s="55" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="86">
-        <f>'TW-L'!C10</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="85">
-        <f>'TW-L'!$C$4</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="85">
-        <f>'TW-L'!$C$5</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="81">
-        <f>I11+Y11+AA11+AF11+AG11</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="82">
-        <f>SUM(J11:X11)</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="82">
-        <f>'TW-L'!N10</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="82">
-        <v>0</v>
-      </c>
-      <c r="L11" s="82">
-        <f>'TW-L'!AC10</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="82">
-        <f>'TW-L'!O10</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="82">
-        <f>'TW-L'!P10</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="82">
-        <f>'TW-L'!Q10</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="82">
-        <f>'TW-L'!R10</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="82">
-        <f>'TW-L'!X10+'TW-L'!Y10</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="82">
-        <f>'TW-L'!U10</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="82">
-        <f>'TW-L'!V10</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="82">
-        <f>'TW-L'!W10</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="82">
-        <f>'TW-L'!X10</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="82">
-        <f>'TW-L'!Y10</f>
-        <v>0</v>
-      </c>
-      <c r="W11" s="82">
-        <f>'TW-L'!AA10</f>
-        <v>0</v>
-      </c>
-      <c r="X11" s="82">
-        <f>'TW-L'!AB10</f>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="82">
-        <f>SUM(Z11:Z11)</f>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="82">
-        <f>'TW-L'!Z10</f>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="82">
-        <f>SUM(AB11:AE11)</f>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="82">
-        <f>'TW-L'!AR10+'TW-L'!AS10</f>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="82">
-        <f>'TW-L'!AT10+'TW-L'!AU10</f>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="82">
-        <f>'TW-L'!AV10+'TW-L'!AW10</f>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="82">
-        <f>'TW-L'!AY10</f>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="82">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="83">
-        <f>'TW-L'!AQ10</f>
-        <v>0</v>
-      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="82"/>
+      <c r="J11" s="82"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="82"/>
+      <c r="M11" s="82"/>
+      <c r="N11" s="82"/>
+      <c r="O11" s="82"/>
+      <c r="P11" s="82"/>
+      <c r="Q11" s="82"/>
+      <c r="R11" s="82"/>
+      <c r="S11" s="82"/>
+      <c r="T11" s="82"/>
+      <c r="U11" s="82"/>
+      <c r="V11" s="82"/>
+      <c r="W11" s="82"/>
+      <c r="X11" s="82"/>
+      <c r="Y11" s="82"/>
+      <c r="Z11" s="82"/>
+      <c r="AA11" s="82"/>
+      <c r="AB11" s="82"/>
+      <c r="AC11" s="82"/>
+      <c r="AD11" s="82"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="83"/>
     </row>
     <row r="12" s="55" customFormat="1" spans="1:33">
       <c r="A12" s="77"/>
-      <c r="B12" s="55" t="str">
-        <f>PN!$B$9</f>
-        <v>CUS1516</v>
-      </c>
-      <c r="C12" s="55" t="str">
-        <f>PN!B9</f>
-        <v>CUS1516</v>
-      </c>
-      <c r="D12" s="55" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="86">
-        <f>'TW-L'!C11</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="85">
-        <f>'TW-L'!$C$4</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="85">
-        <f>'TW-L'!$C$5</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="81">
-        <f>I12+Y12+AA12+AF12+AG12</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="82">
-        <f>SUM(J12:X12)</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="82">
-        <f>'TW-L'!N11</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="82">
-        <v>0</v>
-      </c>
-      <c r="L12" s="82">
-        <f>'TW-L'!AC11</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="82">
-        <f>'TW-L'!O11</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="82">
-        <f>'TW-L'!P11</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="82">
-        <f>'TW-L'!Q11</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="82">
-        <f>'TW-L'!R11</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="82">
-        <f>'TW-L'!X11+'TW-L'!Y11</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="82">
-        <f>'TW-L'!U11</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="82">
-        <f>'TW-L'!V11</f>
-        <v>0</v>
-      </c>
-      <c r="T12" s="82">
-        <f>'TW-L'!W11</f>
-        <v>0</v>
-      </c>
-      <c r="U12" s="82">
-        <f>'TW-L'!X11</f>
-        <v>0</v>
-      </c>
-      <c r="V12" s="82">
-        <f>'TW-L'!Y11</f>
-        <v>0</v>
-      </c>
-      <c r="W12" s="82">
-        <f>'TW-L'!AA11</f>
-        <v>0</v>
-      </c>
-      <c r="X12" s="82">
-        <f>'TW-L'!AB11</f>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="82">
-        <f>SUM(Z12:Z12)</f>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="82">
-        <f>'TW-L'!Z11</f>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="82">
-        <f>SUM(AB12:AE12)</f>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="82">
-        <f>'TW-L'!AR11+'TW-L'!AS11</f>
-        <v>0</v>
-      </c>
-      <c r="AC12" s="82">
-        <f>'TW-L'!AT11+'TW-L'!AU11</f>
-        <v>0</v>
-      </c>
-      <c r="AD12" s="82">
-        <f>'TW-L'!AV11+'TW-L'!AW11</f>
-        <v>0</v>
-      </c>
-      <c r="AE12" s="82">
-        <f>'TW-L'!AY11</f>
-        <v>0</v>
-      </c>
-      <c r="AF12" s="82">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="83">
-        <f>'TW-L'!AQ11</f>
-        <v>0</v>
-      </c>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="86"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="83"/>
     </row>
     <row r="13" s="55" customFormat="1" spans="1:33">
       <c r="A13" s="77"/>
@@ -5825,13 +5447,13 @@
   <sheetData>
     <row r="2" spans="1:71">
       <c r="A2" s="6" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D2" s="6"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:71">
       <c r="A3" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="9"/>
@@ -5861,7 +5483,7 @@
       <c r="AB3"/>
       <c r="AC3"/>
       <c r="AD3" s="10" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="AE3" s="11"/>
       <c r="AF3" s="11"/>
@@ -5904,7 +5526,7 @@
     <row r="4" ht="15" customHeight="1" spans="1:71">
       <c r="A4"/>
       <c r="B4" s="13" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="15"/>
@@ -5975,7 +5597,7 @@
     <row r="5" ht="15.75" customHeight="1" spans="1:71">
       <c r="A5"/>
       <c r="B5" s="13" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="15"/>
@@ -6046,7 +5668,7 @@
     <row r="6" s="1" customFormat="1" ht="17.25" customHeight="1" spans="1:71">
       <c r="D6" s="3"/>
       <c r="M6" s="17" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="N6" s="18"/>
       <c r="O6" s="18"/>
@@ -6065,7 +5687,7 @@
       <c r="AB6" s="18"/>
       <c r="AC6" s="19"/>
       <c r="AD6" s="20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="AE6" s="18"/>
       <c r="AF6" s="18"/>
@@ -6075,14 +5697,14 @@
       <c r="AJ6" s="18"/>
       <c r="AK6" s="18"/>
       <c r="AL6" s="21" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AM6" s="22"/>
       <c r="AN6" s="22"/>
       <c r="AO6" s="22"/>
       <c r="AP6" s="23"/>
       <c r="AQ6" s="17" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="AR6" s="18"/>
       <c r="AS6" s="18"/>
@@ -6095,7 +5717,7 @@
       <c r="AZ6" s="24"/>
       <c r="BA6" s="25"/>
       <c r="BB6" s="26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="BC6" s="18"/>
       <c r="BD6" s="18"/>
@@ -6109,205 +5731,205 @@
     </row>
     <row r="7" s="2" customFormat="1" ht="57.5" customHeight="1" spans="1:71">
       <c r="A7" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="29" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="H7" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="I7" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="J7" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="M7" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="N7" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="O7" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="P7" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="S7" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="T7" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="U7" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="V7" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="X7" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y7" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z7" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="AA7" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB7" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC7" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="32" t="s">
+      <c r="AD7" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="M7" s="31" t="s">
+      <c r="AE7" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="AF7" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="O7" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="P7" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="S7" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="T7" s="29" t="s">
+      <c r="AG7" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="U7" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="V7" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="X7" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y7" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z7" s="29" t="s">
+      <c r="AH7" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="AA7" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB7" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="AC7" s="29" t="s">
+      <c r="AI7" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="AD7" s="29" t="s">
+      <c r="AJ7" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="AE7" s="29" t="s">
+      <c r="AK7" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="AF7" s="29" t="s">
+      <c r="AL7" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="AG7" s="29" t="s">
+      <c r="AM7" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="AH7" s="29" t="s">
+      <c r="AN7" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="AI7" s="29" t="s">
+      <c r="AO7" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="AJ7" s="29" t="s">
+      <c r="AP7" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="AK7" s="29" t="s">
+      <c r="AQ7" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="AL7" s="29" t="s">
+      <c r="AR7" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="AM7" s="29" t="s">
+      <c r="AS7" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="AN7" s="29" t="s">
+      <c r="AT7" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="AO7" s="29" t="s">
+      <c r="AU7" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AP7" s="29" t="s">
+      <c r="AV7" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="AQ7" s="29" t="s">
+      <c r="AW7" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="AR7" s="29" t="s">
+      <c r="AX7" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="AS7" s="29" t="s">
+      <c r="AY7" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AZ7" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="BA7" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="BB7" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="BC7" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="AX7" s="35" t="s">
+      <c r="BD7" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="AY7" s="29" t="s">
+      <c r="BE7" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="AZ7" s="36" t="s">
+      <c r="BF7" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="BA7" s="36" t="s">
+      <c r="BG7" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="BB7" s="29" t="s">
+      <c r="BH7" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="BC7" s="29" t="s">
+      <c r="BI7" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="BD7" s="29" t="s">
+      <c r="BJ7" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="BE7" s="29" t="s">
+      <c r="BK7" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="BF7" s="29" t="s">
+      <c r="BL7" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="BG7" s="29" t="s">
+      <c r="BM7" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN7" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="BH7" s="29" t="s">
+      <c r="BO7" s="37" t="s">
         <v>144</v>
-      </c>
-      <c r="BI7" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="BJ7" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="BK7" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="BL7" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="BM7" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="BN7" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="BO7" s="37" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="8" ht="14.25" customHeight="1" spans="1:71">
